--- a/04_Маршрутные_карты/Перечень_маршрутных_карт.xlsx
+++ b/04_Маршрутные_карты/Перечень_маршрутных_карт.xlsx
@@ -534,14 +534,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 455×60×2,9, L=1550</t>
+          <t>Деталь 1550×455×60</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.29</v>
+        <v>1.13</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -596,14 +596,14 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Профиль резиновый 1200×346,4, L=6276,8</t>
+          <t>Полотно гибкое (резина), s=5</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.45</v>
+        <v>1.14</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -627,14 +627,14 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Деталь 250,5×244×130,5</t>
+          <t>Панель гнутая, s=4,7</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.97</v>
+        <v>0.63</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -658,14 +658,14 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Деталь 250,5×230,2×139</t>
+          <t>Панель гнутая, s=4,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.97</v>
+        <v>0.63</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -720,14 +720,14 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Профиль резиновый 171×32,8, L=5700</t>
+          <t>Полотно гибкое (резина), s=4,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.43</v>
+        <v>1.03</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -751,14 +751,14 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Стержень ⌀63, L=1026</t>
+          <t>Деталь 1026×63×63</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
         <v>27</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.53</v>
+        <v>1.07</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -782,14 +782,14 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀108×13,1, L=1338</t>
+          <t>Деталь 1338×108×108</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.28</v>
+        <v>1.1</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -813,14 +813,14 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Профиль сплошной 105×15, L=1260</t>
+          <t>Деталь 1260×105×15</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.28</v>
+        <v>1.1</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -968,14 +968,14 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 168,7×62×2, L=5720</t>
+          <t>Панель гнутая, s=4,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.43</v>
+        <v>1.03</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 168,7×62×2, L=5720</t>
+          <t>Панель гнутая, s=4,8</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.43</v>
+        <v>1.03</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1154,14 +1154,14 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 451×105×3,3, L=3500</t>
+          <t>Деталь 3500×451×105</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.36</v>
+        <v>1.37</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -1185,14 +1185,14 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 451×105×3,3, L=3500</t>
+          <t>Деталь 3500×451×105</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.36</v>
+        <v>1.37</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1402,14 +1402,14 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 451×105×3,5, L=2105</t>
+          <t>Деталь 2105×451×105</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.31</v>
+        <v>1.2</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -1433,14 +1433,14 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 451×105×3,5, L=2105</t>
+          <t>Деталь 2105×451×105</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.31</v>
+        <v>1.2</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -1712,14 +1712,14 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Деталь 1561,4×1250×138,1</t>
+          <t>Панель гнутая, s=5</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>1.13</v>
+        <v>0.8</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -1867,14 +1867,14 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 250×138,1×1,8, L=1561,4</t>
+          <t>Панель гнутая, s=4,9</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.29</v>
+        <v>0.72</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -2332,14 +2332,14 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀30×2, L=894</t>
+          <t>Деталь 894×30×30</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.27</v>
+        <v>1.05</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -2363,14 +2363,14 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 600×85×2,8, L=3004</t>
+          <t>Деталь 3004×600×85</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0.34</v>
+        <v>1.31</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -2394,14 +2394,14 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 600×85×2,8, L=3004</t>
+          <t>Деталь 3004×600×85</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0.34</v>
+        <v>1.31</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -2456,14 +2456,14 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 600×85×2,9, L=2500</t>
+          <t>Деталь 2500×600×85</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.32</v>
+        <v>1.25</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -2487,14 +2487,14 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Деталь 1561,4×1000×138,1</t>
+          <t>Панель гнутая, s=5</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>1.13</v>
+        <v>0.78</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -2518,14 +2518,14 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Деталь 1561,4×1000×138,1</t>
+          <t>Панель гнутая, s=5</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>1.13</v>
+        <v>0.78</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -2580,14 +2580,14 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 80×45×4,9, L=2128</t>
+          <t>Деталь 2128×80×45</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.31</v>
+        <v>1.21</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -2611,14 +2611,14 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀50×3,3, L=1410</t>
+          <t>Деталь 1410×50×50</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>0.29</v>
+        <v>1.12</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -2642,14 +2642,14 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀50×3,3, L=1207</t>
+          <t>Деталь 1207×50×50</t>
         </is>
       </c>
       <c r="E71" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>0.28</v>
+        <v>1.09</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -2952,14 +2952,14 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Деталь 80×80×60,6</t>
+          <t>Панель гнутая, s=3,6</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -2983,14 +2983,14 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Деталь 126,5×80×80</t>
+          <t>Панель гнутая, s=3,9</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>0.96</v>
+        <v>0.6</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Деталь 223,4×80×80</t>
+          <t>Панель гнутая, s=3,9</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0.97</v>
+        <v>0.62</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -3231,14 +3231,14 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Стержень ⌀20, L=150</t>
+          <t>Деталь 150×20×20</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
         <v>24</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>0.47</v>
+        <v>0.96</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -3262,14 +3262,14 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀480,9×1,3, L=1510</t>
+          <t>Панель гнутая, s=2</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>0.29</v>
+        <v>0.73</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -3324,14 +3324,14 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 120×55×2,4, L=1510</t>
+          <t>Деталь 1510×120×55</t>
         </is>
       </c>
       <c r="E93" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>0.29</v>
+        <v>1.13</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
@@ -3417,14 +3417,14 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Стержень ⌀95, L=2052</t>
+          <t>Деталь 2052×95×95</t>
         </is>
       </c>
       <c r="E96" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>0.6</v>
+        <v>1.19</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -3510,14 +3510,14 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Стержень ⌀75, L=1660</t>
+          <t>Деталь 1660×75×75</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>0.57</v>
+        <v>1.15</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -3541,14 +3541,14 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Профиль сплошной 100×20, L=326</t>
+          <t>Деталь 326×100×20</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>0.25</v>
+        <v>0.98</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -3572,14 +3572,14 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Деталь 336×192×140</t>
+          <t>Панель гнутая, s=2</t>
         </is>
       </c>
       <c r="E101" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0.98</v>
+        <v>0.63</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -3603,14 +3603,14 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Деталь 340×192×140</t>
+          <t>Панель гнутая, s=1,9</t>
         </is>
       </c>
       <c r="E102" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>0.98</v>
+        <v>0.63</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -3696,14 +3696,14 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Стержень ⌀36, L=500</t>
+          <t>Деталь 500×36×36</t>
         </is>
       </c>
       <c r="E105" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>0.49</v>
+        <v>1</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -3727,14 +3727,14 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Деталь 1550×1027,1×95,1</t>
+          <t>Панель гнутая, s=3</t>
         </is>
       </c>
       <c r="E106" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>1.13</v>
+        <v>0.78</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -3789,14 +3789,14 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 80×60×3,8, L=1320</t>
+          <t>Деталь 1320×80×60</t>
         </is>
       </c>
       <c r="E108" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>0.28</v>
+        <v>1.1</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -3820,14 +3820,14 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Деталь 946×696×30</t>
+          <t>Панель гнутая, s=3</t>
         </is>
       </c>
       <c r="E109" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>1.06</v>
+        <v>0.71</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -3851,14 +3851,14 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Деталь 764×455×105</t>
+          <t>Панель гнутая, s=5,9</t>
         </is>
       </c>
       <c r="E110" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -3882,14 +3882,14 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Деталь 764×455×105</t>
+          <t>Панель гнутая, s=5,9</t>
         </is>
       </c>
       <c r="E111" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
@@ -4068,14 +4068,14 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀40×2,4, L=850</t>
+          <t>Деталь 850×40×40</t>
         </is>
       </c>
       <c r="E117" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>0.27</v>
+        <v>1.04</v>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
@@ -4099,14 +4099,14 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀40×2,4, L=850</t>
+          <t>Деталь 850×40×40</t>
         </is>
       </c>
       <c r="E118" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0.27</v>
+        <v>1.04</v>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
@@ -4130,14 +4130,14 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀36×2,4, L=1050</t>
+          <t>Деталь 1050×36×36</t>
         </is>
       </c>
       <c r="E119" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>0.28</v>
+        <v>1.07</v>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
@@ -4161,14 +4161,14 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Труба ⌀36×2,1, L=350</t>
+          <t>Деталь 350×36×36</t>
         </is>
       </c>
       <c r="E120" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>0.25</v>
+        <v>0.98</v>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
@@ -4192,14 +4192,14 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 60×41,4×1,2, L=248,4</t>
+          <t>Панель гнутая, s=3,7</t>
         </is>
       </c>
       <c r="E121" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>0.25</v>
+        <v>0.62</v>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
@@ -4254,14 +4254,14 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Деталь 1184×500×50</t>
+          <t>Панель гнутая, s=4,9</t>
         </is>
       </c>
       <c r="E123" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>1.09</v>
+        <v>0.72</v>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
@@ -4285,14 +4285,14 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Труба профильная 35,4×19×1,4, L=1174</t>
+          <t>Деталь 1174×35,4×19</t>
         </is>
       </c>
       <c r="E124" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>0.28</v>
+        <v>1.09</v>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
@@ -4316,14 +4316,14 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Стержень ⌀16, L=500</t>
+          <t>Деталь 500×16×16</t>
         </is>
       </c>
       <c r="E125" s="2" t="n">
         <v>2</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>0.49</v>
+        <v>1</v>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
@@ -4347,14 +4347,14 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Деталь 86×80×60</t>
+          <t>Панель гнутая, s=2,7</t>
         </is>
       </c>
       <c r="E126" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="F169" s="3" t="n">
-        <v>215.5</v>
+        <v>235.6</v>
       </c>
     </row>
   </sheetData>
